--- a/server/assets/template.xlsx
+++ b/server/assets/template.xlsx
@@ -21,18 +21,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
   <si>
-    <t xml:space="preserve">(Дата сотавления)</t>
+    <t xml:space="preserve">(Дата соcтавления)</t>
   </si>
   <si>
     <t xml:space="preserve">(Место составления)</t>
   </si>
   <si>
     <t xml:space="preserve">Акт №</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Н-ПР-</t>
   </si>
   <si>
     <t xml:space="preserve">О порче товара по неосторожности, транспортировке, производстве работ внутри склада, нарушение правил хранения товара на складе.</t>
@@ -510,39 +507,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -558,267 +555,267 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1551,7 +1548,7 @@
       <c r="S11" s="8"/>
       <c r="T11" s="9" t="str">
         <f aca="false">CONCATENATE(AH11,AT11)</f>
-        <v>Н-ПР-</v>
+        <v/>
       </c>
       <c r="U11" s="10" t="s">
         <v>2</v>
@@ -1568,9 +1565,7 @@
       <c r="AE11" s="10"/>
       <c r="AF11" s="10"/>
       <c r="AG11" s="10"/>
-      <c r="AH11" s="10" t="s">
-        <v>3</v>
-      </c>
+      <c r="AH11" s="10"/>
       <c r="AI11" s="10"/>
       <c r="AJ11" s="10"/>
       <c r="AK11" s="10"/>
@@ -1990,7 +1985,7 @@
     </row>
     <row r="19" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2507,7 +2502,7 @@
     </row>
     <row r="26" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -2673,7 +2668,7 @@
     </row>
     <row r="28" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AL28" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
@@ -2810,7 +2805,7 @@
     </row>
     <row r="31" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -2835,7 +2830,7 @@
       <c r="V31" s="19"/>
       <c r="W31" s="19"/>
       <c r="X31" s="20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31" s="20"/>
       <c r="Z31" s="20"/>
@@ -2884,7 +2879,7 @@
       <c r="BQ31" s="19"/>
       <c r="BR31" s="19"/>
       <c r="BS31" s="21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BT31" s="21"/>
       <c r="BU31" s="21"/>
@@ -3228,7 +3223,7 @@
     </row>
     <row r="36" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -3640,7 +3635,7 @@
     </row>
     <row r="42" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B42" s="26"/>
       <c r="C42" s="26"/>
@@ -4014,7 +4009,7 @@
     </row>
     <row r="48" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
@@ -4205,7 +4200,7 @@
     </row>
     <row r="51" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B51" s="33"/>
       <c r="C51" s="33"/>
@@ -5192,7 +5187,7 @@
     <row r="63" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="36"/>
       <c r="B63" s="37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C63" s="37"/>
       <c r="D63" s="37"/>
@@ -5222,7 +5217,7 @@
       <c r="AB63" s="32"/>
       <c r="AC63" s="36"/>
       <c r="AD63" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE63" s="38"/>
       <c r="AF63" s="38"/>
@@ -5360,7 +5355,7 @@
     <row r="65" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="36"/>
       <c r="B65" s="39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C65" s="39"/>
       <c r="D65" s="39"/>
@@ -5549,7 +5544,7 @@
       <c r="AI67" s="42"/>
       <c r="AJ67" s="43"/>
       <c r="AK67" s="44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL67" s="44"/>
       <c r="AM67" s="44"/>
@@ -5576,7 +5571,7 @@
       <c r="BH67" s="45"/>
       <c r="BI67" s="46"/>
       <c r="BJ67" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BK67" s="44"/>
       <c r="BL67" s="44"/>
@@ -5763,7 +5758,7 @@
     </row>
     <row r="70" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B70" s="38"/>
       <c r="C70" s="38"/>
@@ -6062,7 +6057,7 @@
       <c r="I74" s="42"/>
       <c r="J74" s="42"/>
       <c r="K74" s="44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L74" s="44"/>
       <c r="M74" s="44"/>
@@ -6087,7 +6082,7 @@
       <c r="AI74" s="42"/>
       <c r="AJ74" s="43"/>
       <c r="AK74" s="44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL74" s="44"/>
       <c r="AM74" s="44"/>
@@ -6111,7 +6106,7 @@
       <c r="BH74" s="45"/>
       <c r="BI74" s="46"/>
       <c r="BJ74" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BK74" s="44"/>
       <c r="BL74" s="44"/>
@@ -6210,7 +6205,7 @@
     </row>
     <row r="76" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B76" s="38"/>
       <c r="C76" s="38"/>
@@ -6500,7 +6495,7 @@
       <c r="I80" s="42"/>
       <c r="J80" s="42"/>
       <c r="K80" s="44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L80" s="44"/>
       <c r="M80" s="44"/>
@@ -6525,7 +6520,7 @@
       <c r="AI80" s="42"/>
       <c r="AJ80" s="43"/>
       <c r="AK80" s="44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL80" s="44"/>
       <c r="AM80" s="44"/>
@@ -6549,7 +6544,7 @@
       <c r="BH80" s="45"/>
       <c r="BI80" s="46"/>
       <c r="BJ80" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BK80" s="44"/>
       <c r="BL80" s="44"/>
@@ -6639,7 +6634,7 @@
     </row>
     <row r="82" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B82" s="38"/>
       <c r="C82" s="38"/>
@@ -6879,7 +6874,7 @@
       <c r="I86" s="42"/>
       <c r="J86" s="42"/>
       <c r="K86" s="44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L86" s="44"/>
       <c r="M86" s="44"/>
@@ -6904,7 +6899,7 @@
       <c r="AI86" s="42"/>
       <c r="AJ86" s="42"/>
       <c r="AK86" s="44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL86" s="44"/>
       <c r="AM86" s="44"/>
@@ -6928,7 +6923,7 @@
       <c r="BH86" s="45"/>
       <c r="BI86" s="45"/>
       <c r="BJ86" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BK86" s="44"/>
       <c r="BL86" s="44"/>
@@ -7169,7 +7164,7 @@
       <c r="I90" s="42"/>
       <c r="J90" s="42"/>
       <c r="K90" s="44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L90" s="44"/>
       <c r="M90" s="44"/>
@@ -7194,7 +7189,7 @@
       <c r="AI90" s="42"/>
       <c r="AJ90" s="42"/>
       <c r="AK90" s="44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL90" s="44"/>
       <c r="AM90" s="44"/>
@@ -7218,7 +7213,7 @@
       <c r="BH90" s="45"/>
       <c r="BI90" s="45"/>
       <c r="BJ90" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BK90" s="44"/>
       <c r="BL90" s="44"/>
@@ -7452,7 +7447,7 @@
     <row r="94" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C94" s="43"/>
       <c r="K94" s="44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L94" s="44"/>
       <c r="M94" s="44"/>
@@ -7477,7 +7472,7 @@
       <c r="AI94" s="42"/>
       <c r="AJ94" s="42"/>
       <c r="AK94" s="44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL94" s="44"/>
       <c r="AM94" s="44"/>
@@ -7501,7 +7496,7 @@
       <c r="BH94" s="45"/>
       <c r="BI94" s="45"/>
       <c r="BJ94" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BK94" s="44"/>
       <c r="BL94" s="44"/>
@@ -7655,7 +7650,7 @@
     </row>
     <row r="98" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B98" s="53"/>
       <c r="C98" s="53"/>
@@ -8008,7 +8003,7 @@
       <c r="W102" s="32"/>
       <c r="X102" s="32"/>
       <c r="Y102" s="54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z102" s="54"/>
       <c r="AA102" s="54"/>
@@ -8068,7 +8063,7 @@
     </row>
     <row r="103" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B103" s="38"/>
       <c r="C103" s="38"/>
@@ -8268,7 +8263,7 @@
       <c r="AG105" s="32"/>
       <c r="AH105" s="32"/>
       <c r="AI105" s="59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ105" s="59"/>
       <c r="AK105" s="59"/>
@@ -8318,7 +8313,7 @@
     </row>
     <row r="106" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B106" s="38"/>
       <c r="C106" s="38"/>
@@ -8486,7 +8481,7 @@
       <c r="A108" s="62"/>
       <c r="B108" s="62"/>
       <c r="C108" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D108" s="38"/>
       <c r="E108" s="38"/>
@@ -8494,7 +8489,7 @@
       <c r="G108" s="62"/>
       <c r="H108" s="62"/>
       <c r="I108" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J108" s="38"/>
       <c r="K108" s="38"/>
@@ -8502,7 +8497,7 @@
       <c r="M108" s="62"/>
       <c r="N108" s="62"/>
       <c r="O108" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P108" s="38"/>
       <c r="Q108" s="38"/>
@@ -8980,7 +8975,7 @@
     </row>
     <row r="114" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B114" s="38"/>
       <c r="C114" s="38"/>
@@ -9006,7 +9001,7 @@
       <c r="W114" s="38"/>
       <c r="X114" s="32"/>
       <c r="Y114" s="54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Z114" s="54"/>
       <c r="AA114" s="54"/>
@@ -9150,7 +9145,7 @@
       <c r="A116" s="62"/>
       <c r="B116" s="62"/>
       <c r="C116" s="67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D116" s="67"/>
       <c r="E116" s="67"/>
@@ -9164,7 +9159,7 @@
       <c r="M116" s="62"/>
       <c r="N116" s="62"/>
       <c r="O116" s="68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P116" s="68"/>
       <c r="Q116" s="68"/>
@@ -9427,7 +9422,7 @@
       <c r="BB121" s="70"/>
       <c r="BC121" s="70"/>
       <c r="BD121" s="71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BE121" s="71"/>
       <c r="BF121" s="71"/>
@@ -10031,7 +10026,7 @@
     <row r="130" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="75"/>
       <c r="B130" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C130" s="38"/>
       <c r="D130" s="38"/>
@@ -10099,7 +10094,7 @@
       <c r="B132" s="62"/>
       <c r="C132" s="62"/>
       <c r="D132" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E132" s="26"/>
       <c r="F132" s="26"/>
@@ -10118,7 +10113,7 @@
       <c r="V132" s="62"/>
       <c r="W132" s="62"/>
       <c r="X132" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y132" s="26"/>
       <c r="Z132" s="26"/>
@@ -10137,7 +10132,7 @@
       <c r="AP132" s="62"/>
       <c r="AQ132" s="62"/>
       <c r="AR132" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AS132" s="26"/>
       <c r="AT132" s="26"/>
@@ -10156,7 +10151,7 @@
       <c r="BJ132" s="62"/>
       <c r="BK132" s="62"/>
       <c r="BL132" s="76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="BM132" s="76"/>
       <c r="BN132" s="76"/>
@@ -10330,7 +10325,7 @@
     </row>
     <row r="136" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B136" s="26"/>
       <c r="C136" s="26"/>
@@ -10562,7 +10557,7 @@
       <c r="I141" s="42"/>
       <c r="J141" s="42"/>
       <c r="K141" s="44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L141" s="44"/>
       <c r="M141" s="44"/>
@@ -10587,7 +10582,7 @@
       <c r="AI141" s="42"/>
       <c r="AJ141" s="42"/>
       <c r="AK141" s="44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL141" s="44"/>
       <c r="AM141" s="44"/>
@@ -10611,7 +10606,7 @@
       <c r="BH141" s="45"/>
       <c r="BI141" s="45"/>
       <c r="BJ141" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BK141" s="44"/>
       <c r="BL141" s="44"/>
